--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>84.68977287890843</v>
+        <v>13.76208809282262</v>
       </c>
       <c r="D2" t="n">
-        <v>45.62693140250335</v>
+        <v>7.414376352906793</v>
       </c>
       <c r="E2" t="n">
-        <v>5.101155833172648</v>
+        <v>0.8289378228905546</v>
       </c>
       <c r="F2" t="n">
-        <v>13.95893282737421</v>
+        <v>2.268326584448308</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>74.48746121256313</v>
+        <v>12.10421244704151</v>
       </c>
       <c r="D3" t="n">
-        <v>17.70906574775493</v>
+        <v>2.877723184010177</v>
       </c>
       <c r="E3" t="n">
-        <v>5.101155833172648</v>
+        <v>0.8289378228905546</v>
       </c>
       <c r="F3" t="n">
-        <v>13.95893282737421</v>
+        <v>2.268326584448308</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
